--- a/uploads/기사관리_2024.xlsx
+++ b/uploads/기사관리_2024.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\HanMi\ERP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CDA7500-2DFE-49E7-8C05-07CDD6C9FEC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2839013E-A199-458A-BE00-1BBB33F4DE69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{66348461-5697-4C24-A8D1-6ED51936E14B}"/>
+    <workbookView xWindow="22932" yWindow="216" windowWidth="23256" windowHeight="12456" xr2:uid="{66348461-5697-4C24-A8D1-6ED51936E14B}"/>
   </bookViews>
   <sheets>
     <sheet name="profile" sheetId="1" r:id="rId1"/>
@@ -2354,7 +2354,7 @@
         <v>46387</v>
       </c>
       <c r="H2" s="6">
-        <v>35886</v>
+        <v>35887</v>
       </c>
       <c r="I2" s="9" t="s">
         <v>593</v>
